--- a/02-Excel/Most Common Excel Functions.xlsx
+++ b/02-Excel/Most Common Excel Functions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Videos\New Excel Vids\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0-AI\DataAnalyst\DataAnalyst_Portfolio\02-Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2778AD4C-FE08-4D04-90A2-0B20CBCFB73C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" xr2:uid="{4D63D859-9D5E-47C3-BFA4-698B9CB0A943}"/>
+    <workbookView xWindow="3510" yWindow="2310" windowWidth="21750" windowHeight="13890" activeTab="4" xr2:uid="{4D63D859-9D5E-47C3-BFA4-698B9CB0A943}"/>
   </bookViews>
   <sheets>
     <sheet name="Aggregate Functions" sheetId="1" r:id="rId1"/>
@@ -260,7 +260,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -638,9 +638,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F755BAE-46B7-44C6-B523-F7823EC890B3}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultColWidth="17.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="17.625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>3</v>
       </c>
@@ -663,7 +663,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>45292</v>
       </c>
@@ -686,7 +686,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>45293</v>
       </c>
@@ -709,7 +709,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>45294</v>
       </c>
@@ -732,7 +732,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>45295</v>
       </c>
@@ -755,7 +755,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>45296</v>
       </c>
@@ -775,7 +775,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>45297</v>
       </c>
@@ -798,7 +798,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>45298</v>
       </c>
@@ -821,7 +821,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>45299</v>
       </c>
@@ -844,7 +844,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>45300</v>
       </c>
@@ -867,7 +867,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>45301</v>
       </c>
@@ -890,7 +890,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="E12" s="3" t="s">
         <v>26</v>
       </c>
@@ -909,9 +909,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B8E5D47-ED21-4655-B4D2-4810F992D9C9}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="18.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>29</v>
       </c>
@@ -928,7 +928,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>33</v>
       </c>
@@ -936,7 +936,7 @@
         <v>45306</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>34</v>
       </c>
@@ -944,7 +944,7 @@
         <v>45342</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>35</v>
       </c>
@@ -952,7 +952,7 @@
         <v>45376</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>36</v>
       </c>
@@ -960,7 +960,7 @@
         <v>45412</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>37</v>
       </c>
@@ -968,12 +968,12 @@
         <v>45427</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B7" s="1">
         <v>501</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
         <v>69</v>
       </c>
@@ -986,15 +986,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F333D182-B195-4BB6-A068-B235FD477B4C}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.453125" customWidth="1"/>
-    <col min="2" max="2" width="16.7265625" customWidth="1"/>
-    <col min="3" max="3" width="17.1796875" customWidth="1"/>
+    <col min="1" max="1" width="19.5" customWidth="1"/>
+    <col min="2" max="2" width="16.75" customWidth="1"/>
+    <col min="3" max="3" width="17.125" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>38</v>
       </c>
@@ -1008,22 +1008,22 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>42</v>
       </c>
@@ -1036,9 +1036,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{352C8367-A508-43F0-B38F-D583DEBEA0DE}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultColWidth="18.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="18.5" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>43</v>
       </c>
@@ -1055,7 +1055,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>49</v>
       </c>
@@ -1069,7 +1069,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>50</v>
       </c>
@@ -1083,7 +1083,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>51</v>
       </c>
@@ -1097,7 +1097,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>52</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>48</v>
       </c>
@@ -1125,7 +1125,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>53</v>
       </c>
@@ -1138,13 +1138,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7435F50D-7B4D-4FA5-B99A-D12076C39E82}">
   <dimension ref="A1:F31"/>
-  <sheetFormatPr defaultColWidth="18.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="18.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="23" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>59</v>
       </c>
@@ -1164,7 +1164,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>3668</v>
       </c>
@@ -1177,7 +1177,7 @@
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>4965</v>
       </c>
@@ -1190,7 +1190,7 @@
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>4836</v>
       </c>
@@ -1203,7 +1203,7 @@
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>9291</v>
       </c>
@@ -1216,7 +1216,7 @@
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>8580</v>
       </c>
@@ -1229,7 +1229,7 @@
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>4734</v>
       </c>
@@ -1242,7 +1242,7 @@
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>1342</v>
       </c>
@@ -1255,7 +1255,7 @@
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>6827</v>
       </c>
@@ -1268,7 +1268,7 @@
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>5450</v>
       </c>
@@ -1281,7 +1281,7 @@
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>3676</v>
       </c>
@@ -1294,7 +1294,7 @@
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>3836</v>
       </c>
@@ -1307,7 +1307,7 @@
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>9713</v>
       </c>
@@ -1320,7 +1320,7 @@
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>8682</v>
       </c>
@@ -1333,7 +1333,7 @@
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>9655</v>
       </c>
@@ -1346,7 +1346,7 @@
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>54</v>
       </c>
@@ -1354,7 +1354,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>55</v>
       </c>
@@ -1362,7 +1362,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>56</v>
       </c>
@@ -1370,7 +1370,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>57</v>
       </c>
@@ -1378,7 +1378,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>58</v>
       </c>
@@ -1386,7 +1386,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>9</v>
       </c>
@@ -1394,7 +1394,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
         <v>0.1</v>
       </c>
@@ -1402,7 +1402,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
         <v>0.15</v>
       </c>
@@ -1410,7 +1410,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
         <v>0.05</v>
       </c>
@@ -1418,7 +1418,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
         <v>0.2</v>
       </c>
